--- a/data/trans_orig/IMC_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2007</t>
+          <t>Población con sobrepeso u obesidad en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116014</t>
+          <t>117600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154524</t>
+          <t>155566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t>52450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81751</t>
+          <t>81810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177484</t>
+          <t>180472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227757</t>
+          <t>227791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332784</t>
+          <t>331742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>371294</t>
+          <t>369708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383836</t>
+          <t>383777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412546</t>
+          <t>413137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725139</t>
+          <t>725105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775412</t>
+          <t>772424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>309640</t>
+          <t>310233</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363665</t>
+          <t>363296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145870</t>
+          <t>145077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192445</t>
+          <t>189779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>468235</t>
+          <t>470564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542306</t>
+          <t>542997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366465</t>
+          <t>366834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420490</t>
+          <t>419897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429038</t>
+          <t>431704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475613</t>
+          <t>476406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>809306</t>
+          <t>808615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883377</t>
+          <t>881048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389499</t>
+          <t>384220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>436021</t>
+          <t>435121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>243763</t>
+          <t>244784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295748</t>
+          <t>295002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>643444</t>
+          <t>645248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720331</t>
+          <t>718112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200012</t>
+          <t>200912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246534</t>
+          <t>251813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391107</t>
+          <t>391853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443092</t>
+          <t>442071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602557</t>
+          <t>604776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679444</t>
+          <t>677640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>347521</t>
+          <t>347003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>389354</t>
+          <t>391452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260148</t>
+          <t>259036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303909</t>
+          <t>305712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>621933</t>
+          <t>620689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>683454</t>
+          <t>683585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126909</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168742</t>
+          <t>169260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203804</t>
+          <t>202001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247565</t>
+          <t>248677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340523</t>
+          <t>340392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402044</t>
+          <t>403288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281875</t>
+          <t>281962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>313004</t>
+          <t>312959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251975</t>
+          <t>251644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289266</t>
+          <t>289393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>542901</t>
+          <t>543397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>594884</t>
+          <t>593032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70882</t>
+          <t>70927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102011</t>
+          <t>101924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105712</t>
+          <t>105585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143003</t>
+          <t>143334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183980</t>
+          <t>185832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235963</t>
+          <t>235467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203121</t>
+          <t>200873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>229971</t>
+          <t>230114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251412</t>
+          <t>251099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>280350</t>
+          <t>278485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>459638</t>
+          <t>461910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502574</t>
+          <t>502850</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57159</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84009</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59281</t>
+          <t>61146</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88219</t>
+          <t>88532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>123911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167123</t>
+          <t>164851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143001</t>
+          <t>142723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164989</t>
+          <t>165648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236085</t>
+          <t>234518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266148</t>
+          <t>264475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384777</t>
+          <t>386254</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>423504</t>
+          <t>425867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>52256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135283</t>
+          <t>133806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1870667</t>
+          <t>1866586</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1980387</t>
+          <t>1979827</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1514167</t>
+          <t>1515368</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1636648</t>
+          <t>1632779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3408281</t>
+          <t>3418548</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3574539</t>
+          <t>3579984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1263692</t>
+          <t>1264252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1373412</t>
+          <t>1377493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1696330</t>
+          <t>1700199</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1818811</t>
+          <t>1817610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3002518</t>
+          <t>2997073</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3168776</t>
+          <t>3158509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2012</t>
+          <t>Población con sobrepeso u obesidad en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122416</t>
+          <t>123890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163529</t>
+          <t>163050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>71794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104403</t>
+          <t>105746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206458</t>
+          <t>205508</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>257210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285665</t>
+          <t>286144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326778</t>
+          <t>325304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318632</t>
+          <t>317289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350712</t>
+          <t>351241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614509</t>
+          <t>615019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>665771</t>
+          <t>666721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>333607</t>
+          <t>331755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387420</t>
+          <t>384660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205628</t>
+          <t>203547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253781</t>
+          <t>253938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549084</t>
+          <t>550525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>623314</t>
+          <t>625036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294792</t>
+          <t>297552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348605</t>
+          <t>350457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340230</t>
+          <t>340073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388383</t>
+          <t>390464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652909</t>
+          <t>651187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727139</t>
+          <t>725698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>447812</t>
+          <t>447596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>496473</t>
+          <t>493665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>311051</t>
+          <t>312794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>366885</t>
+          <t>365711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>773025</t>
+          <t>772881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>849724</t>
+          <t>847907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170415</t>
+          <t>173223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219076</t>
+          <t>219292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323192</t>
+          <t>324366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>379026</t>
+          <t>377283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507241</t>
+          <t>509058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583940</t>
+          <t>584084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>436194</t>
+          <t>436334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>479185</t>
+          <t>482034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>318341</t>
+          <t>321073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367818</t>
+          <t>372100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>767778</t>
+          <t>764474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>838212</t>
+          <t>836575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,56%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125238</t>
+          <t>122389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168229</t>
+          <t>168089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230410</t>
+          <t>226128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279887</t>
+          <t>277155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364439</t>
+          <t>366076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434873</t>
+          <t>438177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>301492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>338051</t>
+          <t>337665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293060</t>
+          <t>293982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>332617</t>
+          <t>333595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>609751</t>
+          <t>609037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>662102</t>
+          <t>661445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81319</t>
+          <t>81705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117547</t>
+          <t>117878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103815</t>
+          <t>102837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143372</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193701</t>
+          <t>194358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246052</t>
+          <t>246766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>242198</t>
+          <t>241260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>269930</t>
+          <t>269807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252095</t>
+          <t>251591</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>281246</t>
+          <t>282173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>504299</t>
+          <t>503206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>543971</t>
+          <t>542927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47652</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76803</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88238</t>
+          <t>89282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127910</t>
+          <t>129003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173989</t>
+          <t>173777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198829</t>
+          <t>198860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>253752</t>
+          <t>255519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284671</t>
+          <t>283352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>436059</t>
+          <t>435829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>474753</t>
+          <t>476068</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>53509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83109</t>
+          <t>81342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>95734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135743</t>
+          <t>135973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2139359</t>
+          <t>2139579</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2254473</t>
+          <t>2253686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1791319</t>
+          <t>1790187</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1908600</t>
+          <t>1912198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3964416</t>
+          <t>3972883</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4131460</t>
+          <t>4136184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1105867</t>
+          <t>1106654</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1220981</t>
+          <t>1220761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1498942</t>
+          <t>1495344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1616223</t>
+          <t>1617355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2636422</t>
+          <t>2631698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2803466</t>
+          <t>2794999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2016</t>
+          <t>Población con sobrepeso u obesidad en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85780</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121943</t>
+          <t>121219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104455</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166984</t>
+          <t>165321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213886</t>
+          <t>213366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282797</t>
+          <t>283521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>318960</t>
+          <t>319657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277861</t>
+          <t>280626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311530</t>
+          <t>312354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573170</t>
+          <t>573690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>620072</t>
+          <t>621735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235908</t>
+          <t>236007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281660</t>
+          <t>284367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185532</t>
+          <t>186954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229058</t>
+          <t>229848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>435062</t>
+          <t>435246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>498540</t>
+          <t>501354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293682</t>
+          <t>290975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339434</t>
+          <t>339335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311417</t>
+          <t>310627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354943</t>
+          <t>353521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617276</t>
+          <t>614462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680754</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>376564</t>
+          <t>377340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427519</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>254527</t>
+          <t>250242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>302592</t>
+          <t>299861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645174</t>
+          <t>644448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>714454</t>
+          <t>715972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226971</t>
+          <t>227074</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277926</t>
+          <t>277150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335369</t>
+          <t>338100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>383434</t>
+          <t>387719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577997</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647277</t>
+          <t>648003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>412066</t>
+          <t>415539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>460498</t>
+          <t>461311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316204</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>365969</t>
+          <t>367948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745294</t>
+          <t>743765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>814719</t>
+          <t>812113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166487</t>
+          <t>165674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214919</t>
+          <t>211446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260472</t>
+          <t>258493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310237</t>
+          <t>312346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438707</t>
+          <t>441313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>508132</t>
+          <t>509661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329461</t>
+          <t>329536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>370185</t>
+          <t>367299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>307361</t>
+          <t>308651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>351197</t>
+          <t>350161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>644794</t>
+          <t>649037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>706136</t>
+          <t>709175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93592</t>
+          <t>96478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134316</t>
+          <t>134241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122650</t>
+          <t>123686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231487</t>
+          <t>228448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292829</t>
+          <t>288586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>245256</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>273465</t>
+          <t>272857</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>233867</t>
+          <t>234164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>269252</t>
+          <t>269758</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>489105</t>
+          <t>489141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>535536</t>
+          <t>533826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>72872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>77742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113633</t>
+          <t>113336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130092</t>
+          <t>131802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176523</t>
+          <t>176487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162454</t>
+          <t>162225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186802</t>
+          <t>186266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229823</t>
+          <t>230934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266241</t>
+          <t>267026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>404643</t>
+          <t>402086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>445978</t>
+          <t>445650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68001</t>
+          <t>68230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67547</t>
+          <t>66762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103965</t>
+          <t>102854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118265</t>
+          <t>118593</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159600</t>
+          <t>162157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1935748</t>
+          <t>1932044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2047170</t>
+          <t>2043113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1690039</t>
+          <t>1687084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1806197</t>
+          <t>1809568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3656367</t>
+          <t>3644058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3817441</t>
+          <t>3813354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1226746</t>
+          <t>1230803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1338168</t>
+          <t>1341872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1536131</t>
+          <t>1532760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1652289</t>
+          <t>1655244</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2798803</t>
+          <t>2802890</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2959877</t>
+          <t>2972186</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2023</t>
+          <t>Población con sobrepeso u obesidad en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163943</t>
+          <t>165169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51731</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88339</t>
+          <t>88444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161805</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238666</t>
+          <t>243570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231587</t>
+          <t>230361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296161</t>
+          <t>295375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215909</t>
+          <t>215804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>252443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461112</t>
+          <t>456208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537973</t>
+          <t>539693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189822</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242769</t>
+          <t>244224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181665</t>
+          <t>181456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323862</t>
+          <t>334490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398534</t>
+          <t>399391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576658</t>
+          <t>567521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179428</t>
+          <t>177973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232375</t>
+          <t>230649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182431</t>
+          <t>171803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324628</t>
+          <t>324837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>351832</t>
+          <t>360969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>529956</t>
+          <t>529099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>279873</t>
+          <t>279374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327227</t>
+          <t>327671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192162</t>
+          <t>192249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229019</t>
+          <t>229429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>481213</t>
+          <t>484000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>543787</t>
+          <t>542911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204666</t>
+          <t>204222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>252020</t>
+          <t>252519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308846</t>
+          <t>308436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345703</t>
+          <t>345616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525971</t>
+          <t>526847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588545</t>
+          <t>585758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>594840</t>
+          <t>591369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>795819</t>
+          <t>796385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>326950</t>
+          <t>323785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>368205</t>
+          <t>366716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>920246</t>
+          <t>915938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1228610</t>
+          <t>1219364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82463</t>
+          <t>81897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283442</t>
+          <t>286913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293698</t>
+          <t>295187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334953</t>
+          <t>338118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311576</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>619940</t>
+          <t>624248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392246</t>
+          <t>390930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>430398</t>
+          <t>429981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>311192</t>
+          <t>308788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344469</t>
+          <t>343156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>713330</t>
+          <t>712010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>763274</t>
+          <t>761787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>116131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153866</t>
+          <t>155182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186403</t>
+          <t>187716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219680</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>313710</t>
+          <t>315197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363654</t>
+          <t>364974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>257670</t>
+          <t>256891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>283213</t>
+          <t>282442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>408911</t>
+          <t>408518</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>543764</t>
+          <t>547762</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>682833</t>
+          <t>681770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>839141</t>
+          <t>833963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73772</t>
+          <t>74543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99315</t>
+          <t>100094</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43317</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178170</t>
+          <t>178563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104925</t>
+          <t>110103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261233</t>
+          <t>262296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178266</t>
+          <t>178316</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202022</t>
+          <t>202267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255424</t>
+          <t>255835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281223</t>
+          <t>280106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439363</t>
+          <t>441057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475094</t>
+          <t>475222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65218</t>
+          <t>64973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>88924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>90692</t>
+          <t>91809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116491</t>
+          <t>116080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>164061</t>
+          <t>163933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>199792</t>
+          <t>198098</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2087287</t>
+          <t>2088119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2493642</t>
+          <t>2474728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1795803</t>
+          <t>1806140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2223087</t>
+          <t>2215162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3939613</t>
+          <t>3946098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4497479</t>
+          <t>4540917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>904596</t>
+          <t>923510</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1310951</t>
+          <t>1310119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1277091</t>
+          <t>1285016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1704375</t>
+          <t>1694038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2400937</t>
+          <t>2357499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2958803</t>
+          <t>2952318</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117600</t>
+          <t>115875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155566</t>
+          <t>153923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>51672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81810</t>
+          <t>80499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180472</t>
+          <t>177834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227791</t>
+          <t>227682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331742</t>
+          <t>333385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>369708</t>
+          <t>371433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383777</t>
+          <t>385088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413137</t>
+          <t>413915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725105</t>
+          <t>725214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772424</t>
+          <t>775062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>310233</t>
+          <t>311323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363296</t>
+          <t>368046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>145966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>190183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>470564</t>
+          <t>466171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542997</t>
+          <t>538553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366834</t>
+          <t>362084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419897</t>
+          <t>418807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431704</t>
+          <t>431300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476406</t>
+          <t>475517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808615</t>
+          <t>813059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881048</t>
+          <t>885441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>384220</t>
+          <t>386684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>435121</t>
+          <t>437154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244784</t>
+          <t>244608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295002</t>
+          <t>295690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645248</t>
+          <t>647116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>718112</t>
+          <t>720660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200912</t>
+          <t>198879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>251813</t>
+          <t>249349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391853</t>
+          <t>391165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442071</t>
+          <t>442247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604776</t>
+          <t>602228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>677640</t>
+          <t>675772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>347003</t>
+          <t>347817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>391452</t>
+          <t>391418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259036</t>
+          <t>262675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305712</t>
+          <t>304628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>620689</t>
+          <t>619384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>683585</t>
+          <t>683184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124811</t>
+          <t>124845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169260</t>
+          <t>168446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202001</t>
+          <t>203085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>245038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340392</t>
+          <t>340793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403288</t>
+          <t>404593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281962</t>
+          <t>282940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312959</t>
+          <t>313558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251644</t>
+          <t>251075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289393</t>
+          <t>288827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>543397</t>
+          <t>544947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>593032</t>
+          <t>594295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70927</t>
+          <t>70328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101924</t>
+          <t>100946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105585</t>
+          <t>106151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143334</t>
+          <t>143903</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185832</t>
+          <t>184569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235467</t>
+          <t>233917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200873</t>
+          <t>202499</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>230114</t>
+          <t>230858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251099</t>
+          <t>251262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>278485</t>
+          <t>280376</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>461910</t>
+          <t>462809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502850</t>
+          <t>503573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>56272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123911</t>
+          <t>123188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164851</t>
+          <t>163952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142723</t>
+          <t>141312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165648</t>
+          <t>165186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234518</t>
+          <t>234765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264475</t>
+          <t>265387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386254</t>
+          <t>386647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425867</t>
+          <t>424864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>62017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52256</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82213</t>
+          <t>81966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94193</t>
+          <t>95196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>133806</t>
+          <t>133413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1866586</t>
+          <t>1869898</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1979827</t>
+          <t>1981608</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1515368</t>
+          <t>1519462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1632779</t>
+          <t>1631473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3418548</t>
+          <t>3422415</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3579984</t>
+          <t>3589263</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1264252</t>
+          <t>1262471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1377493</t>
+          <t>1374181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1700199</t>
+          <t>1701505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1817610</t>
+          <t>1813516</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2997073</t>
+          <t>2987794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3158509</t>
+          <t>3154642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123890</t>
+          <t>122564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163050</t>
+          <t>162696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71794</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105746</t>
+          <t>103735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205508</t>
+          <t>206497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257210</t>
+          <t>258356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286144</t>
+          <t>286498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325304</t>
+          <t>326630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>317289</t>
+          <t>319300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>351241</t>
+          <t>350703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615019</t>
+          <t>613873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666721</t>
+          <t>665732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,33%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>331755</t>
+          <t>330649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384660</t>
+          <t>382656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203547</t>
+          <t>205195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253938</t>
+          <t>255044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550525</t>
+          <t>551403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>625036</t>
+          <t>619013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297552</t>
+          <t>299556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350457</t>
+          <t>351563</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340073</t>
+          <t>338967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390464</t>
+          <t>388816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651187</t>
+          <t>657210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725698</t>
+          <t>724820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>447596</t>
+          <t>447888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>493922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>312794</t>
+          <t>310950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365711</t>
+          <t>365420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>772881</t>
+          <t>769942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>847907</t>
+          <t>848047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173223</t>
+          <t>172966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219292</t>
+          <t>219000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324366</t>
+          <t>324657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>377283</t>
+          <t>379127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509058</t>
+          <t>508918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584084</t>
+          <t>587023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>436334</t>
+          <t>434953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>482034</t>
+          <t>478626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321073</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>372100</t>
+          <t>369603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>764474</t>
+          <t>768664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>836575</t>
+          <t>839678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122389</t>
+          <t>125797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168089</t>
+          <t>169470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226128</t>
+          <t>228625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277155</t>
+          <t>279529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366076</t>
+          <t>362973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>438177</t>
+          <t>433987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301492</t>
+          <t>302853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>337665</t>
+          <t>338563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293982</t>
+          <t>292288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>333595</t>
+          <t>332699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>609037</t>
+          <t>607738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>661445</t>
+          <t>658950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81705</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117878</t>
+          <t>116517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102837</t>
+          <t>103733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>144144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194358</t>
+          <t>196853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246766</t>
+          <t>248065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>241260</t>
+          <t>242207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>269807</t>
+          <t>269136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251591</t>
+          <t>251637</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282173</t>
+          <t>280154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>503206</t>
+          <t>502268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>542927</t>
+          <t>543443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>61104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46725</t>
+          <t>48744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>77261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89282</t>
+          <t>88766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129003</t>
+          <t>129941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173777</t>
+          <t>174292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198860</t>
+          <t>199050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255519</t>
+          <t>254747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283352</t>
+          <t>285308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>435829</t>
+          <t>434400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476068</t>
+          <t>476528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>35891</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61164</t>
+          <t>60649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53509</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81342</t>
+          <t>82114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95734</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>137402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2139579</t>
+          <t>2142227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2253686</t>
+          <t>2257017</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1790187</t>
+          <t>1792324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1912198</t>
+          <t>1914143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3972883</t>
+          <t>3960643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4136184</t>
+          <t>4128547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1106654</t>
+          <t>1103323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1220761</t>
+          <t>1218113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1495344</t>
+          <t>1493399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1617355</t>
+          <t>1615218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2631698</t>
+          <t>2639335</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2794999</t>
+          <t>2807239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85083</t>
+          <t>84273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121219</t>
+          <t>121551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,82 +6706,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>86449</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71782</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>102997</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22,61%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>26,94%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>188945</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>165444</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>212830</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>21,02%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>86449</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>69962</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>101690</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>188945</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>165321</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>213366</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283521</t>
+          <t>283189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>319657</t>
+          <t>320467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,82 +6819,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>295867</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>279319</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>310534</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>77,39%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>73,06%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>81,22%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>598111</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>574226</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>621612</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>75,99%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>78,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>295867</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>280626</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>312354</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>81,7%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>598111</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>573690</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>621735</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>72,89%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236007</t>
+          <t>233850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>284367</t>
+          <t>282691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186954</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229848</t>
+          <t>229571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>435246</t>
+          <t>432938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>501354</t>
+          <t>496072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290975</t>
+          <t>292651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339335</t>
+          <t>341492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310627</t>
+          <t>310904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353521</t>
+          <t>354243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>614462</t>
+          <t>619744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>682878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>377340</t>
+          <t>376861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427416</t>
+          <t>427509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>250242</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299861</t>
+          <t>305257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644448</t>
+          <t>643451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>715972</t>
+          <t>716941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227074</t>
+          <t>226981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277150</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338100</t>
+          <t>332704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>387719</t>
+          <t>384165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576479</t>
+          <t>575510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648003</t>
+          <t>649000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>415539</t>
+          <t>414249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>461311</t>
+          <t>460363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>314095</t>
+          <t>315520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367948</t>
+          <t>366882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>743765</t>
+          <t>742345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>812113</t>
+          <t>813679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165674</t>
+          <t>166622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>212736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258493</t>
+          <t>259559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312346</t>
+          <t>310921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441313</t>
+          <t>439747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>509661</t>
+          <t>511081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329536</t>
+          <t>329308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>367299</t>
+          <t>369284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308651</t>
+          <t>302966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350161</t>
+          <t>348563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>649037</t>
+          <t>649686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>709175</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96478</t>
+          <t>94493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134241</t>
+          <t>134469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123686</t>
+          <t>125284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>170881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228448</t>
+          <t>228637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288586</t>
+          <t>287937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>245256</t>
+          <t>245683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>272857</t>
+          <t>273897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>234164</t>
+          <t>236401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>269758</t>
+          <t>270242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>489141</t>
+          <t>492359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>533826</t>
+          <t>536652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72872</t>
+          <t>72445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77742</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113336</t>
+          <t>111099</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131802</t>
+          <t>128976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176487</t>
+          <t>173269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162225</t>
+          <t>162898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186266</t>
+          <t>186876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230934</t>
+          <t>230755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>267026</t>
+          <t>267693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>402086</t>
+          <t>401567</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>445650</t>
+          <t>445738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44189</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68230</t>
+          <t>67557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>66762</t>
+          <t>66095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>102854</t>
+          <t>103033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118593</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162157</t>
+          <t>162676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1932044</t>
+          <t>1929506</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2043113</t>
+          <t>2045342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1687084</t>
+          <t>1687468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1809568</t>
+          <t>1800615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3644058</t>
+          <t>3651727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3813354</t>
+          <t>3812538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1230803</t>
+          <t>1228574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1341872</t>
+          <t>1344410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1532760</t>
+          <t>1541713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1655244</t>
+          <t>1654860</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2802890</t>
+          <t>2803706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2972186</t>
+          <t>2964517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>131381</t>
+          <t>124261</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>95504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165169</t>
+          <t>160755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68332</t>
+          <t>80453</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>62038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>102236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>199713</t>
+          <t>204714</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160085</t>
+          <t>169240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243570</t>
+          <t>242272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264149</t>
+          <t>272748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230361</t>
+          <t>236254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295375</t>
+          <t>301505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>235916</t>
+          <t>272706</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215804</t>
+          <t>250923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252443</t>
+          <t>291121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>500065</t>
+          <t>545454</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456208</t>
+          <t>507896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539693</t>
+          <t>580928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395530</t>
+          <t>397009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395530</t>
+          <t>397009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395530</t>
+          <t>397009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>304248</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304248</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304248</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>699778</t>
+          <t>750168</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>699778</t>
+          <t>750168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>699778</t>
+          <t>750168</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>219163</t>
+          <t>240045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191548</t>
+          <t>211015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244224</t>
+          <t>267572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232195</t>
+          <t>189106</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181456</t>
+          <t>166578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>334490</t>
+          <t>211714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>451358</t>
+          <t>429151</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>399391</t>
+          <t>394347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>567521</t>
+          <t>465566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203034</t>
+          <t>233198</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177973</t>
+          <t>205671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230649</t>
+          <t>262228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>274098</t>
+          <t>303979</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171803</t>
+          <t>281371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324837</t>
+          <t>326507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>477132</t>
+          <t>537177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360969</t>
+          <t>500762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>529099</t>
+          <t>571981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422197</t>
+          <t>473243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422197</t>
+          <t>473243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422197</t>
+          <t>473243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506293</t>
+          <t>493085</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>506293</t>
+          <t>493085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>506293</t>
+          <t>493085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>928490</t>
+          <t>966328</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>928490</t>
+          <t>966328</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>928490</t>
+          <t>966328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>302627</t>
+          <t>347446</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>279374</t>
+          <t>322607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327671</t>
+          <t>372716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>210470</t>
+          <t>255484</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192249</t>
+          <t>235593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229429</t>
+          <t>276991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>513098</t>
+          <t>602930</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484000</t>
+          <t>569071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542911</t>
+          <t>634662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>229266</t>
+          <t>266528</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204222</t>
+          <t>241258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>252519</t>
+          <t>291367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>327395</t>
+          <t>361104</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308436</t>
+          <t>339597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345616</t>
+          <t>380995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>556660</t>
+          <t>627633</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>526847</t>
+          <t>595901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585758</t>
+          <t>661492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>531893</t>
+          <t>613974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>531893</t>
+          <t>613974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>531893</t>
+          <t>613974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>537865</t>
+          <t>616588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>537865</t>
+          <t>616588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>537865</t>
+          <t>616588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1069758</t>
+          <t>1230563</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1069758</t>
+          <t>1230563</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1069758</t>
+          <t>1230563</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>682433</t>
+          <t>479721</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>591369</t>
+          <t>455154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>796385</t>
+          <t>506245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>346980</t>
+          <t>373511</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323785</t>
+          <t>349483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366716</t>
+          <t>393274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1029413</t>
+          <t>853232</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>915938</t>
+          <t>817472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1219364</t>
+          <t>885122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>195849</t>
+          <t>209087</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>182563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>286913</t>
+          <t>233654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>314923</t>
+          <t>343310</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295187</t>
+          <t>323547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>338118</t>
+          <t>367338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>510773</t>
+          <t>552397</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320822</t>
+          <t>520507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>624248</t>
+          <t>588157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>878282</t>
+          <t>688808</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>878282</t>
+          <t>688808</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>878282</t>
+          <t>688808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>661903</t>
+          <t>716821</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>661903</t>
+          <t>716821</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>661903</t>
+          <t>716821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1540186</t>
+          <t>1405629</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1540186</t>
+          <t>1405629</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1540186</t>
+          <t>1405629</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>411576</t>
+          <t>443521</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390930</t>
+          <t>424726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429981</t>
+          <t>464921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>327083</t>
+          <t>365284</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308788</t>
+          <t>347082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343156</t>
+          <t>383913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>738658</t>
+          <t>808805</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>712010</t>
+          <t>782595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761787</t>
+          <t>837523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134536</t>
+          <t>148205</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116131</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155182</t>
+          <t>167000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>203789</t>
+          <t>224873</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187716</t>
+          <t>206244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222084</t>
+          <t>243075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>338326</t>
+          <t>373078</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315197</t>
+          <t>344360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364974</t>
+          <t>399288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546112</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546112</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546112</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>590157</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>590157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>590157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1076984</t>
+          <t>1181883</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1076984</t>
+          <t>1181883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1076984</t>
+          <t>1181883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>270591</t>
+          <t>295798</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>256891</t>
+          <t>278936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>282442</t>
+          <t>308473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475405</t>
+          <t>297246</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>408518</t>
+          <t>283133</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>547762</t>
+          <t>309680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>745996</t>
+          <t>593044</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>681770</t>
+          <t>572345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>833963</t>
+          <t>612436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86394</t>
+          <t>98089</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>85414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100094</t>
+          <t>114951</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>111676</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39319</t>
+          <t>106800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178563</t>
+          <t>133347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>198070</t>
+          <t>217323</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110103</t>
+          <t>197931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262296</t>
+          <t>238022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>356985</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>356985</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>356985</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>587081</t>
+          <t>416480</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>587081</t>
+          <t>416480</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>587081</t>
+          <t>416480</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>944066</t>
+          <t>810367</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>944066</t>
+          <t>810367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>944066</t>
+          <t>810367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>190313</t>
+          <t>207578</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178316</t>
+          <t>194052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202267</t>
+          <t>220611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>293170</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255835</t>
+          <t>279971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280106</t>
+          <t>305408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>458866</t>
+          <t>500749</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>441057</t>
+          <t>481358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475222</t>
+          <t>519559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>86090</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64973</t>
+          <t>73057</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88924</t>
+          <t>99616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103362</t>
+          <t>112824</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116080</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>180289</t>
+          <t>198913</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>163933</t>
+          <t>180103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198098</t>
+          <t>218304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>267240</t>
+          <t>293668</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267240</t>
+          <t>293668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>267240</t>
+          <t>293668</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>371915</t>
+          <t>405994</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>371915</t>
+          <t>405994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>371915</t>
+          <t>405994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>639155</t>
+          <t>699662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>639155</t>
+          <t>699662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>639155</t>
+          <t>699662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2088119</t>
+          <t>2075818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2474728</t>
+          <t>2201794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1806140</t>
+          <t>1798777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2215162</t>
+          <t>1905633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3946098</t>
+          <t>3911796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4540917</t>
+          <t>4078433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1190155</t>
+          <t>1313944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>923510</t>
+          <t>1250521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1310119</t>
+          <t>1376497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1571159</t>
+          <t>1738031</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1285016</t>
+          <t>1686653</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1694038</t>
+          <t>1793509</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2761314</t>
+          <t>3051975</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2357499</t>
+          <t>2966168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2952318</t>
+          <t>3132805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
